--- a/manufacturing_forms/018_manufacturing_quality_assurance_job_application--manufacturing_forms.xlsx
+++ b/manufacturing_forms/018_manufacturing_quality_assurance_job_application--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>contact_details_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>job_satisfactions</t>
+          <t>job_satisfactions_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Job Satisfactions</t>
+          <t>Job Satisfactions 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>references</t>
+          <t>references_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>References</t>
+          <t>References 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>references</t>
+          <t>references_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>References</t>
+          <t>References 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -753,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,34 +781,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>contact_details_choices</t>
+          <t>contact_details_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>contact_details_choices</t>
+          <t>contact_details_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>contact_details_2_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
